--- a/data_lake/behavior/FINRA Margin.xlsx
+++ b/data_lake/behavior/FINRA Margin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A150899B-EFCD-4E81-924B-3110CFE78FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA264A1D-952D-214E-8165-53F19D492319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17200" yWindow="780" windowWidth="18800" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MARGBLNC" sheetId="1" r:id="rId1"/>
@@ -73,15 +73,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -106,7 +106,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -114,7 +114,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +122,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,46 +146,46 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -487,20 +487,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H355"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H356"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>35431</v>
       </c>
@@ -560,7 +560,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>35462</v>
       </c>
@@ -597,7 +597,7 @@
       </c>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>35490</v>
       </c>
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>35521</v>
       </c>
@@ -641,7 +641,7 @@
       </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>35551</v>
       </c>
@@ -663,7 +663,7 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>35582</v>
       </c>
@@ -685,7 +685,7 @@
       </c>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>35612</v>
       </c>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>35643</v>
       </c>
@@ -729,7 +729,7 @@
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>35674</v>
       </c>
@@ -751,7 +751,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>35704</v>
       </c>
@@ -773,7 +773,7 @@
       </c>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>35735</v>
       </c>
@@ -795,7 +795,7 @@
       </c>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>35765</v>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>35796</v>
       </c>
@@ -839,7 +839,7 @@
       </c>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>35827</v>
       </c>
@@ -861,7 +861,7 @@
       </c>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>35855</v>
       </c>
@@ -883,7 +883,7 @@
       </c>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>35886</v>
       </c>
@@ -905,7 +905,7 @@
       </c>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>35916</v>
       </c>
@@ -927,7 +927,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>35947</v>
       </c>
@@ -949,7 +949,7 @@
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>35977</v>
       </c>
@@ -971,7 +971,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>36008</v>
       </c>
@@ -993,7 +993,7 @@
       </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>36039</v>
       </c>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>36069</v>
       </c>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>36100</v>
       </c>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>36130</v>
       </c>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>36161</v>
       </c>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>36192</v>
       </c>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>36220</v>
       </c>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>36251</v>
       </c>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>36281</v>
       </c>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>36312</v>
       </c>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>36342</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>36373</v>
       </c>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>36404</v>
       </c>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>36434</v>
       </c>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>36465</v>
       </c>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>36495</v>
       </c>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>36526</v>
       </c>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>36557</v>
       </c>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>36586</v>
       </c>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>36617</v>
       </c>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>36647</v>
       </c>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>36678</v>
       </c>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>36708</v>
       </c>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>36739</v>
       </c>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>36770</v>
       </c>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>36800</v>
       </c>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>36831</v>
       </c>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>36861</v>
       </c>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>36892</v>
       </c>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>36923</v>
       </c>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>36951</v>
       </c>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>36982</v>
       </c>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>37012</v>
       </c>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>37043</v>
       </c>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>37073</v>
       </c>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>37104</v>
       </c>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>37135</v>
       </c>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>37165</v>
       </c>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>37196</v>
       </c>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>37226</v>
       </c>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>37257</v>
       </c>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>37288</v>
       </c>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>37316</v>
       </c>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>37347</v>
       </c>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>37377</v>
       </c>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>37408</v>
       </c>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>37438</v>
       </c>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>37469</v>
       </c>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>37500</v>
       </c>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>37530</v>
       </c>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>37561</v>
       </c>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>37591</v>
       </c>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>37622</v>
       </c>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>37653</v>
       </c>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>37681</v>
       </c>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>37712</v>
       </c>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>37742</v>
       </c>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>37773</v>
       </c>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>37803</v>
       </c>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>37834</v>
       </c>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>37865</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>37895</v>
       </c>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>37926</v>
       </c>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>37956</v>
       </c>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>37987</v>
       </c>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>38018</v>
       </c>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>38047</v>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>38078</v>
       </c>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>38108</v>
       </c>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>38139</v>
       </c>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>38169</v>
       </c>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>38200</v>
       </c>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="H93" s="7"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>38231</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>38261</v>
       </c>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>38292</v>
       </c>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>38322</v>
       </c>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>38353</v>
       </c>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>38384</v>
       </c>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>38412</v>
       </c>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>38443</v>
       </c>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>38473</v>
       </c>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>38504</v>
       </c>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>38534</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
         <v>38565</v>
       </c>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>38596</v>
       </c>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>38626</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>38657</v>
       </c>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>38687</v>
       </c>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>38718</v>
       </c>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>38749</v>
       </c>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>38777</v>
       </c>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>38808</v>
       </c>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>38838</v>
       </c>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>38869</v>
       </c>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>38899</v>
       </c>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>38930</v>
       </c>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>38961</v>
       </c>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>38991</v>
       </c>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
         <v>39022</v>
       </c>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>39052</v>
       </c>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
         <v>39083</v>
       </c>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>39114</v>
       </c>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
         <v>39142</v>
       </c>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>39173</v>
       </c>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>39203</v>
       </c>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>39234</v>
       </c>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
         <v>39264</v>
       </c>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <v>39295</v>
       </c>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <v>39326</v>
       </c>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <v>39356</v>
       </c>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <v>39387</v>
       </c>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <v>39417</v>
       </c>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <v>39448</v>
       </c>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <v>39479</v>
       </c>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <v>39508</v>
       </c>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <v>39539</v>
       </c>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <v>39569</v>
       </c>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <v>39600</v>
       </c>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <v>39630</v>
       </c>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <v>39661</v>
       </c>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <v>39692</v>
       </c>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <v>39722</v>
       </c>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <v>39753</v>
       </c>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
         <v>39783</v>
       </c>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H145" s="7"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="4">
         <v>39814</v>
       </c>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="4">
         <v>39845</v>
       </c>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
         <v>39873</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="4">
         <v>39904</v>
       </c>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="4">
         <v>39934</v>
       </c>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A151" s="4">
         <v>39965</v>
       </c>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="4">
         <v>39995</v>
       </c>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="H152" s="7"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="4">
         <v>40026</v>
       </c>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="H153" s="7"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="4">
         <v>40057</v>
       </c>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="4">
         <v>40087</v>
       </c>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
         <v>40118</v>
       </c>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="4">
         <v>40148</v>
       </c>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="4">
         <v>40179</v>
       </c>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="4">
         <v>40210</v>
       </c>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H159" s="7"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="4">
         <v>40238</v>
       </c>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H160" s="7"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="4">
         <v>40269</v>
       </c>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="4">
         <v>40299</v>
       </c>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="4">
         <v>40330</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="4">
         <v>40360</v>
       </c>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="4">
         <v>40391</v>
       </c>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="H165" s="7"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A166" s="4">
         <v>40422</v>
       </c>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
         <v>40452</v>
       </c>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="4">
         <v>40483</v>
       </c>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="4">
         <v>40513</v>
       </c>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="H169" s="7"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="4">
         <v>40544</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A171" s="4">
         <v>40575</v>
       </c>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="4">
         <v>40603</v>
       </c>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A173" s="4">
         <v>40634</v>
       </c>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H173" s="7"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A174" s="4">
         <v>40664</v>
       </c>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="4">
         <v>40695</v>
       </c>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="H175" s="7"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A176" s="4">
         <v>40725</v>
       </c>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="4">
         <v>40756</v>
       </c>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
         <v>40787</v>
       </c>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="4">
         <v>40817</v>
       </c>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A180" s="4">
         <v>40848</v>
       </c>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A181" s="4">
         <v>40878</v>
       </c>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
         <v>40909</v>
       </c>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A183" s="4">
         <v>40940</v>
       </c>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H183" s="7"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="4">
         <v>40969</v>
       </c>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="4">
         <v>41000</v>
       </c>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H185" s="7"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A186" s="4">
         <v>41030</v>
       </c>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A187" s="4">
         <v>41061</v>
       </c>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A188" s="4">
         <v>41091</v>
       </c>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
         <v>41122</v>
       </c>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="H189" s="7"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A190" s="4">
         <v>41153</v>
       </c>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="H190" s="7"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="4">
         <v>41183</v>
       </c>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="H191" s="7"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="4">
         <v>41214</v>
       </c>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="4">
         <v>41244</v>
       </c>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="H193" s="7"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="4">
         <v>41275</v>
       </c>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="H194" s="7"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A195" s="4">
         <v>41306</v>
       </c>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="H195" s="7"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A196" s="4">
         <v>41334</v>
       </c>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H196" s="7"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="4">
         <v>41365</v>
       </c>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H197" s="7"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="4">
         <v>41395</v>
       </c>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="H198" s="7"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="4">
         <v>41426</v>
       </c>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="H199" s="7"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
         <v>41456</v>
       </c>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="H200" s="7"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A201" s="4">
         <v>41487</v>
       </c>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="H201" s="7"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="4">
         <v>41518</v>
       </c>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="H202" s="7"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="4">
         <v>41548</v>
       </c>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H203" s="7"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="4">
         <v>41579</v>
       </c>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H204" s="7"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="4">
         <v>41609</v>
       </c>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="4">
         <v>41640</v>
       </c>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="4">
         <v>41671</v>
       </c>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="4">
         <v>41699</v>
       </c>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="4">
         <v>41730</v>
       </c>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="4">
         <v>41760</v>
       </c>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
         <v>41791</v>
       </c>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="4">
         <v>41821</v>
       </c>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="4">
         <v>41852</v>
       </c>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="4">
         <v>41883</v>
       </c>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="H214" s="7"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="4">
         <v>41913</v>
       </c>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="H215" s="7"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="4">
         <v>41944</v>
       </c>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="4">
         <v>41974</v>
       </c>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H217" s="7"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="4">
         <v>42005</v>
       </c>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="H218" s="7"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A219" s="4">
         <v>42036</v>
       </c>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H219" s="7"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="4">
         <v>42064</v>
       </c>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="H220" s="7"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="4">
         <v>42095</v>
       </c>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="H221" s="7"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
         <v>42125</v>
       </c>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="4">
         <v>42156</v>
       </c>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H223" s="7"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="4">
         <v>42186</v>
       </c>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="H224" s="7"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="4">
         <v>42217</v>
       </c>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H225" s="7"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A226" s="4">
         <v>42248</v>
       </c>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="H226" s="7"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A227" s="4">
         <v>42278</v>
       </c>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="H227" s="7"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="4">
         <v>42309</v>
       </c>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="4">
         <v>42339</v>
       </c>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="H229" s="7"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A230" s="4">
         <v>42370</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="H230" s="7"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="4">
         <v>42401</v>
       </c>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H231" s="7"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="4">
         <v>42430</v>
       </c>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H232" s="7"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
         <v>42461</v>
       </c>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="H233" s="7"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A234" s="4">
         <v>42491</v>
       </c>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="H234" s="7"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="4">
         <v>42522</v>
       </c>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="H235" s="7"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A236" s="4">
         <v>42552</v>
       </c>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="H236" s="7"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A237" s="4">
         <v>42583</v>
       </c>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="H237" s="7"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="4">
         <v>42614</v>
       </c>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="H238" s="7"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A239" s="4">
         <v>42644</v>
       </c>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="H239" s="7"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A240" s="4">
         <v>42675</v>
       </c>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="H240" s="7"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A241" s="4">
         <v>42705</v>
       </c>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H241" s="7"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A242" s="4">
         <v>42736</v>
       </c>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="H242" s="7"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A243" s="4">
         <v>42767</v>
       </c>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="H243" s="7"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
         <v>42795</v>
       </c>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="H244" s="7"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="4">
         <v>42826</v>
       </c>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="H245" s="7"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="4">
         <v>42856</v>
       </c>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="H246" s="7"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="4">
         <v>42887</v>
       </c>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="H247" s="7"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A248" s="4">
         <v>42917</v>
       </c>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="H248" s="7"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A249" s="4">
         <v>42948</v>
       </c>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="H249" s="7"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A250" s="4">
         <v>42979</v>
       </c>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H250" s="7"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="4">
         <v>43009</v>
       </c>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="H251" s="7"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="4">
         <v>43040</v>
       </c>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="H252" s="7"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A253" s="4">
         <v>43070</v>
       </c>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="H253" s="7"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A254" s="4">
         <v>43101</v>
       </c>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="H254" s="7"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
         <v>43132</v>
       </c>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="H255" s="7"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="4">
         <v>43160</v>
       </c>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="H256" s="7"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="4">
         <v>43191</v>
       </c>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H257" s="7"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A258" s="4">
         <v>43221</v>
       </c>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="H258" s="7"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="4">
         <v>43252</v>
       </c>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H259" s="7"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="4">
         <v>43282</v>
       </c>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="H260" s="7"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="4">
         <v>43313</v>
       </c>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H261" s="7"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="4">
         <v>43344</v>
       </c>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H262" s="7"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="4">
         <v>43374</v>
       </c>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="H263" s="7"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="4">
         <v>43405</v>
       </c>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H264" s="7"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A265" s="4">
         <v>43435</v>
       </c>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="H265" s="7"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
         <v>43466</v>
       </c>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="H266" s="7"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A267" s="4">
         <v>43497</v>
       </c>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="H267" s="7"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="4">
         <v>43525</v>
       </c>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H268" s="7"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A269" s="4">
         <v>43556</v>
       </c>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="H269" s="7"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A270" s="4">
         <v>43586</v>
       </c>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="H270" s="7"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A271" s="4">
         <v>43617</v>
       </c>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="H271" s="7"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A272" s="4">
         <v>43647</v>
       </c>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="H272" s="7"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A273" s="4">
         <v>43678</v>
       </c>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H273" s="7"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A274" s="4">
         <v>43709</v>
       </c>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H274" s="7"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A275" s="4">
         <v>43739</v>
       </c>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="H275" s="7"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A276" s="4">
         <v>43770</v>
       </c>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H276" s="7"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
         <v>43800</v>
       </c>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A278" s="4">
         <v>43831</v>
       </c>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="4">
         <v>43862</v>
       </c>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="4">
         <v>43891</v>
       </c>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="4">
         <v>43922</v>
       </c>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="4">
         <v>43952</v>
       </c>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="4">
         <v>43983</v>
       </c>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="4">
         <v>44013</v>
       </c>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="4">
         <v>44044</v>
       </c>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="H285" s="7"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="4">
         <v>44075</v>
       </c>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H286" s="7"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="4">
         <v>44105</v>
       </c>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="H287" s="7"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
         <v>44136</v>
       </c>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="H288" s="7"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A289" s="4">
         <v>44166</v>
       </c>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="H289" s="7"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="4">
         <v>44197</v>
       </c>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="H290" s="7"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A291" s="4">
         <v>44228</v>
       </c>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="H291" s="7"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A292" s="4">
         <v>44256</v>
       </c>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="H292" s="7"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A293" s="4">
         <v>44287</v>
       </c>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H293" s="7"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A294" s="4">
         <v>44317</v>
       </c>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="H294" s="7"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="4">
         <v>44348</v>
       </c>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="H295" s="7"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A296" s="4">
         <v>44378</v>
       </c>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="H296" s="7"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A297" s="4">
         <v>44409</v>
       </c>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="H297" s="7"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A298" s="4">
         <v>44440</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H298" s="7"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
         <v>44470</v>
       </c>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H299" s="7"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A300" s="4">
         <v>44501</v>
       </c>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H300" s="7"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A301" s="4">
         <v>44531</v>
       </c>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="H301" s="7"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A302" s="4">
         <v>44562</v>
       </c>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="H302" s="7"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="4">
         <v>44593</v>
       </c>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="H303" s="7"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A304" s="4">
         <v>44621</v>
       </c>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="H304" s="7"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A305" s="4">
         <v>44652</v>
       </c>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="H305" s="7"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A306" s="4">
         <v>44682</v>
       </c>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="H306" s="7"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A307" s="4">
         <v>44713</v>
       </c>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="H307" s="7"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A308" s="4">
         <v>44743</v>
       </c>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="H308" s="7"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A309" s="4">
         <v>44774</v>
       </c>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="H309" s="7"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
         <v>44805</v>
       </c>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="H310" s="7"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A311" s="4">
         <v>44835</v>
       </c>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="H311" s="7"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A312" s="4">
         <v>44866</v>
       </c>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="H312" s="7"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A313" s="4">
         <v>44896</v>
       </c>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H313" s="7"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A314" s="4">
         <v>44927</v>
       </c>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="H314" s="7"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A315" s="4">
         <v>44958</v>
       </c>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="H315" s="7"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A316" s="4">
         <v>44986</v>
       </c>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H316" s="7"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A317" s="4">
         <v>45017</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="H317" s="7"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A318" s="4">
         <v>45047</v>
       </c>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="H318" s="7"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A319" s="4">
         <v>45078</v>
       </c>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="H319" s="7"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A320" s="4">
         <v>45108</v>
       </c>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H320" s="7"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
         <v>45139</v>
       </c>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H321" s="7"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="4">
         <v>45170</v>
       </c>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="H322" s="7"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A323" s="4">
         <v>45200</v>
       </c>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="H323" s="7"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A324" s="4">
         <v>45231</v>
       </c>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="H324" s="7"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A325" s="4">
         <v>45261</v>
       </c>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="H325" s="7"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A326" s="4">
         <v>45292</v>
       </c>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H326" s="7"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A327" s="4">
         <v>45323</v>
       </c>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="H327" s="7"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A328" s="4">
         <v>45352</v>
       </c>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="H328" s="7"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A329" s="4">
         <v>45383</v>
       </c>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H329" s="7"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="4">
         <v>45413</v>
       </c>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="H330" s="7"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A331" s="4">
         <v>45444</v>
       </c>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H331" s="7"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
         <v>45474</v>
       </c>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="H332" s="7"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A333" s="4">
         <v>45505</v>
       </c>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H333" s="7"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A334" s="4">
         <v>45536</v>
       </c>
@@ -8482,7 +8482,7 @@
       </c>
       <c r="H334" s="7"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A335" s="4">
         <v>45566</v>
       </c>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="H335" s="7"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A336" s="4">
         <v>45597</v>
       </c>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="H336" s="7"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A337" s="4">
         <v>45627</v>
       </c>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="H337" s="7"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A338" s="4">
         <v>45658</v>
       </c>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="H338" s="7"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A339" s="4">
         <v>45689</v>
       </c>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="H339" s="7"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A340" s="4">
         <v>45717</v>
       </c>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="H340" s="7"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="4">
         <v>45748</v>
       </c>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="H341" s="7"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A342" s="4">
         <v>45778</v>
       </c>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="H342" s="7"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
         <v>45809</v>
       </c>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="H343" s="7"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A344" s="4">
         <v>45839</v>
       </c>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="H344" s="7"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A345" s="4">
         <v>45870</v>
       </c>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="H345" s="7"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A346" s="4">
         <v>45901</v>
       </c>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H346" s="7"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A347" s="4">
         <v>45931</v>
       </c>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="H347" s="7"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A348" s="4">
         <v>45962</v>
       </c>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="H348" s="7"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A349" s="4">
         <v>45992</v>
       </c>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="H349" s="7"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="4">
         <v>46023</v>
       </c>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H350" s="7"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A351" s="4">
         <v>46054</v>
       </c>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="H351" s="7"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A352" s="4">
         <v>46082</v>
       </c>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="H352" s="7"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A353" s="4">
         <v>46113</v>
       </c>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="H353" s="7"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
         <v>46143</v>
       </c>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="H354" s="7"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A355" s="4">
         <v>46174</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="D355" s="4" t="str">
-        <f t="shared" ref="D355" si="6">IF(
+        <f t="shared" ref="D355:D356" si="6">IF(
  AND(
   B355 &gt;= IF(
          YEAR(B355)&gt;=2007,
@@ -9021,6 +9021,30 @@
         <v>223412</v>
       </c>
     </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A356" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B356" s="5">
+        <v>46260</v>
+      </c>
+      <c r="C356" s="8">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="D356" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E356" s="10">
+        <v>1453832</v>
+      </c>
+      <c r="F356" s="10">
+        <v>207641</v>
+      </c>
+      <c r="G356" s="10">
+        <v>217499</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H354">
     <sortCondition ref="A2:A354"/>
@@ -9033,14 +9057,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5427CE-28CD-4884-AF54-2F1A3787D46D}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="3"/>
-    <col min="2" max="2" width="9.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="8.83203125" style="3"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
@@ -9048,7 +9072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
